--- a/sheet/8614.xlsx
+++ b/sheet/8614.xlsx
@@ -894,10 +894,10 @@
         <v>9</v>
       </c>
       <c r="G13" t="n">
-        <v>3.15</v>
+        <v>9</v>
       </c>
       <c r="H13" t="n">
-        <v>-5.85</v>
+        <v>0</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1334,10 +1334,10 @@
         <v>9</v>
       </c>
       <c r="G25" t="n">
-        <v>3.22</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>-5.78</v>
+        <v>0.14</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1774,10 +1774,10 @@
         <v>9.5</v>
       </c>
       <c r="G37" t="n">
-        <v>3.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H37" t="n">
-        <v>-5.8</v>
+        <v>0.3</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2214,10 +2214,10 @@
         <v>9.5</v>
       </c>
       <c r="G49" t="n">
-        <v>3.25</v>
+        <v>10.23</v>
       </c>
       <c r="H49" t="n">
-        <v>-6.25</v>
+        <v>0.73</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2274,10 +2274,10 @@
         <v>72</v>
       </c>
       <c r="C2" t="n">
-        <v>65.64999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="D2" t="n">
-        <v>-6.35</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="3">
@@ -2290,10 +2290,10 @@
         <v>72</v>
       </c>
       <c r="C3" t="n">
-        <v>65.25999999999999</v>
+        <v>71.17999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>-6.74</v>
+        <v>-0.8200000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -2306,10 +2306,10 @@
         <v>76</v>
       </c>
       <c r="C4" t="n">
-        <v>65.27</v>
+        <v>71.37</v>
       </c>
       <c r="D4" t="n">
-        <v>-10.73</v>
+        <v>-4.63</v>
       </c>
     </row>
     <row r="5">
@@ -2322,10 +2322,10 @@
         <v>76</v>
       </c>
       <c r="C5" t="n">
-        <v>55.26</v>
+        <v>62.24</v>
       </c>
       <c r="D5" t="n">
-        <v>-20.74</v>
+        <v>-13.76</v>
       </c>
     </row>
   </sheetData>

--- a/sheet/8614.xlsx
+++ b/sheet/8614.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:J81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,7 +470,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124</v>
+        <v>465</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125</v>
+        <v>466</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -540,7 +540,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126</v>
+        <v>467</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127</v>
+        <v>468</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -610,7 +610,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128</v>
+        <v>469</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129</v>
+        <v>470</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130</v>
+        <v>471</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131</v>
+        <v>472</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132</v>
+        <v>473</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133</v>
+        <v>474</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134</v>
+        <v>475</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135</v>
+        <v>476</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -910,15 +910,15 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>155</v>
+        <v>477</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BERDIN, GILLYZA L [6565]</t>
+          <t>BERDIN, DENISE G [6595]</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>46143</v>
+        <v>46155</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -934,10 +934,10 @@
         <v>9</v>
       </c>
       <c r="G14" t="n">
-        <v>8.92</v>
+        <v>8.82</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.08</v>
+        <v>-0.18</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -950,21 +950,21 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>156</v>
+        <v>478</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BERDIN, GILLYZA L [6565]</t>
+          <t>BERDIN, DENISE G [6595]</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>46144</v>
+        <v>46156</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -980,21 +980,21 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>157</v>
+        <v>479</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BERDIN, GILLYZA L [6565]</t>
+          <t>BERDIN, DENISE G [6595]</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>46145</v>
+        <v>46157</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1010,34 +1010,24 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>158</v>
+        <v>480</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BERDIN, GILLYZA L [6565]</t>
+          <t>BERDIN, DENISE G [6595]</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>46146</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46158</v>
       </c>
       <c r="F17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1050,34 +1040,24 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>159</v>
+        <v>481</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BERDIN, GILLYZA L [6565]</t>
+          <t>BERDIN, DENISE G [6595]</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>46147</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46159</v>
       </c>
       <c r="F18" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>8.93</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1090,15 +1070,15 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>160</v>
+        <v>482</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BERDIN, GILLYZA L [6565]</t>
+          <t>BERDIN, DENISE G [6595]</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>46148</v>
+        <v>46160</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1114,10 +1094,10 @@
         <v>9</v>
       </c>
       <c r="G19" t="n">
-        <v>8.6</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4</v>
+        <v>-0.62</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1130,15 +1110,15 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>161</v>
+        <v>483</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BERDIN, GILLYZA L [6565]</t>
+          <t>BERDIN, DENISE G [6595]</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>46149</v>
+        <v>46161</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1154,10 +1134,10 @@
         <v>9</v>
       </c>
       <c r="G20" t="n">
-        <v>8.869999999999999</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.13</v>
+        <v>-9</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1170,15 +1150,15 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>162</v>
+        <v>484</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BERDIN, GILLYZA L [6565]</t>
+          <t>BERDIN, DENISE G [6595]</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>46150</v>
+        <v>46162</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1194,10 +1174,10 @@
         <v>9</v>
       </c>
       <c r="G21" t="n">
-        <v>8.869999999999999</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.13</v>
+        <v>-9</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1210,7 +1190,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>163</v>
+        <v>496</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1218,16 +1198,26 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>46151</v>
+        <v>46143</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>8.92</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1240,7 +1230,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>164</v>
+        <v>497</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1248,7 +1238,7 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>46152</v>
+        <v>46144</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -1270,7 +1260,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>165</v>
+        <v>498</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1278,26 +1268,16 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>46153</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46145</v>
       </c>
       <c r="F24" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>8.949999999999999</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1310,7 +1290,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>166</v>
+        <v>499</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1318,7 +1298,7 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>46154</v>
+        <v>46146</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1334,10 +1314,10 @@
         <v>9</v>
       </c>
       <c r="G25" t="n">
-        <v>9.140000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="H25" t="n">
-        <v>0.14</v>
+        <v>-0.1</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1350,19 +1330,19 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>620</v>
+        <v>500</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LAO, ZYRA M [1144]</t>
+          <t>BERDIN, GILLYZA L [6565]</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>46143</v>
+        <v>46147</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>08:30 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1371,13 +1351,13 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="G26" t="n">
-        <v>9.74</v>
+        <v>8.93</v>
       </c>
       <c r="H26" t="n">
-        <v>0.24</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1390,24 +1370,34 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>621</v>
+        <v>501</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LAO, ZYRA M [1144]</t>
+          <t>BERDIN, GILLYZA L [6565]</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>46144</v>
+        <v>46148</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1420,24 +1410,34 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>622</v>
+        <v>502</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>LAO, ZYRA M [1144]</t>
+          <t>BERDIN, GILLYZA L [6565]</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>46145</v>
+        <v>46149</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>-0.13</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1450,19 +1450,19 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>623</v>
+        <v>503</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>LAO, ZYRA M [1144]</t>
+          <t>BERDIN, GILLYZA L [6565]</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>46146</v>
+        <v>46150</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>08:30 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1471,13 +1471,13 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="G29" t="n">
-        <v>9.550000000000001</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="H29" t="n">
-        <v>0.05</v>
+        <v>-0.13</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1490,34 +1490,24 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>624</v>
+        <v>504</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>LAO, ZYRA M [1144]</t>
+          <t>BERDIN, GILLYZA L [6565]</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>46147</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>08:30 AM</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46151</v>
       </c>
       <c r="F30" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-4.93</v>
+        <v>0</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1530,34 +1520,24 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>625</v>
+        <v>505</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>LAO, ZYRA M [1144]</t>
+          <t>BERDIN, GILLYZA L [6565]</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>46148</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>08:30 AM</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46152</v>
       </c>
       <c r="F31" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>9.050000000000001</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.45</v>
+        <v>0</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1570,19 +1550,19 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>626</v>
+        <v>506</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>LAO, ZYRA M [1144]</t>
+          <t>BERDIN, GILLYZA L [6565]</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>08:30 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1591,13 +1571,13 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="G32" t="n">
-        <v>9.5</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1610,19 +1590,19 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>627</v>
+        <v>507</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>LAO, ZYRA M [1144]</t>
+          <t>BERDIN, GILLYZA L [6565]</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>46150</v>
+        <v>46154</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>08:30 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1631,13 +1611,13 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="G33" t="n">
-        <v>9.630000000000001</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="H33" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -1650,24 +1630,34 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>628</v>
+        <v>508</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>LAO, ZYRA M [1144]</t>
+          <t>BERDIN, GILLYZA L [6565]</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>46151</v>
+        <v>46155</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -1680,21 +1670,21 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>629</v>
+        <v>509</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>LAO, ZYRA M [1144]</t>
+          <t>BERDIN, GILLYZA L [6565]</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>46152</v>
+        <v>46156</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1710,19 +1700,19 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>630</v>
+        <v>510</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>LAO, ZYRA M [1144]</t>
+          <t>BERDIN, GILLYZA L [6565]</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>46153</v>
+        <v>46157</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>08:30 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1731,13 +1721,13 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="G36" t="n">
-        <v>9.529999999999999</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="H36" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -1750,34 +1740,24 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>631</v>
+        <v>511</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>LAO, ZYRA M [1144]</t>
+          <t>BERDIN, GILLYZA L [6565]</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>46154</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>08:30 AM</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46158</v>
       </c>
       <c r="F37" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -1790,34 +1770,24 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1240</v>
+        <v>512</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
+          <t>BERDIN, GILLYZA L [6565]</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>46143</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>07:00 PM</t>
-        </is>
+        <v>46159</v>
       </c>
       <c r="F38" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>6.34</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-3.16</v>
+        <v>0</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -1830,24 +1800,34 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1241</v>
+        <v>513</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
+          <t>BERDIN, GILLYZA L [6565]</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>46144</v>
+        <v>46160</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>9.16</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -1860,24 +1840,34 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1242</v>
+        <v>514</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
+          <t>BERDIN, GILLYZA L [6565]</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>46145</v>
+        <v>46161</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -1890,15 +1880,15 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1243</v>
+        <v>515</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
+          <t>BERDIN, GILLYZA L [6565]</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>46146</v>
+        <v>46162</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1907,17 +1897,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>07:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="G41" t="n">
-        <v>6.67</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.83</v>
+        <v>-9</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -1930,34 +1920,34 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1244</v>
+        <v>1705</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
+          <t>LAO, ZYRA M [1144]</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>46147</v>
+        <v>46143</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>07:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F42" t="n">
         <v>9.5</v>
       </c>
       <c r="G42" t="n">
-        <v>8.18</v>
+        <v>9.74</v>
       </c>
       <c r="H42" t="n">
-        <v>-1.32</v>
+        <v>0.24</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -1970,34 +1960,24 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>1245</v>
+        <v>1706</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
+          <t>LAO, ZYRA M [1144]</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>46148</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>07:00 PM</t>
-        </is>
+        <v>46144</v>
       </c>
       <c r="F43" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>-5.12</v>
+        <v>0</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2010,34 +1990,24 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>1246</v>
+        <v>1707</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
+          <t>LAO, ZYRA M [1144]</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>46149</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>07:00 PM</t>
-        </is>
+        <v>46145</v>
       </c>
       <c r="F44" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.7</v>
+        <v>0</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2050,34 +2020,34 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1247</v>
+        <v>1708</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
+          <t>LAO, ZYRA M [1144]</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>46150</v>
+        <v>46146</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>07:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F45" t="n">
         <v>9.5</v>
       </c>
       <c r="G45" t="n">
-        <v>8.77</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.73</v>
+        <v>0.05</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2090,24 +2060,34 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1248</v>
+        <v>1709</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
+          <t>LAO, ZYRA M [1144]</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>46151</v>
+        <v>46147</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2120,24 +2100,34 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1249</v>
+        <v>1710</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
+          <t>LAO, ZYRA M [1144]</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>46152</v>
+        <v>46148</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>-0.45</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2150,34 +2140,34 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1250</v>
+        <v>1711</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
+          <t>LAO, ZYRA M [1144]</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>46153</v>
+        <v>46149</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>07:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F48" t="n">
         <v>9.5</v>
       </c>
       <c r="G48" t="n">
-        <v>8.869999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.63</v>
+        <v>0</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2190,41 +2180,1221 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1251</v>
+        <v>1712</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
+          <t>LAO, ZYRA M [1144]</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>46154</v>
+        <v>46150</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>07:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F49" t="n">
         <v>9.5</v>
       </c>
       <c r="G49" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>1713</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>LAO, ZYRA M [1144]</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>1714</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>LAO, ZYRA M [1144]</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>1715</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>LAO, ZYRA M [1144]</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G52" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>1716</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>LAO, ZYRA M [1144]</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G53" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>1717</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>LAO, ZYRA M [1144]</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>46155</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G54" t="n">
+        <v>9.73</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>1718</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>LAO, ZYRA M [1144]</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G55" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="H55" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>1719</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>LAO, ZYRA M [1144]</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G56" t="n">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>1720</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>LAO, ZYRA M [1144]</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>1721</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>LAO, ZYRA M [1144]</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>1722</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>LAO, ZYRA M [1144]</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G59" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>1723</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>LAO, ZYRA M [1144]</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G60" t="n">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="H60" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>1724</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>LAO, ZYRA M [1144]</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G61" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="H61" t="n">
+        <v>-4.77</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>3658</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G62" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="H62" t="n">
+        <v>-3.16</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>3659</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>3660</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>3661</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G65" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="H65" t="n">
+        <v>-2.83</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>3662</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G66" t="n">
+        <v>8.18</v>
+      </c>
+      <c r="H66" t="n">
+        <v>-1.32</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>3663</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G67" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="H67" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>3664</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G68" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="H68" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>3665</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G69" t="n">
+        <v>8.77</v>
+      </c>
+      <c r="H69" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>3666</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>3667</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>3668</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G72" t="n">
+        <v>8.869999999999999</v>
+      </c>
+      <c r="H72" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>3669</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G73" t="n">
         <v>10.23</v>
       </c>
-      <c r="H49" t="n">
+      <c r="H73" t="n">
         <v>0.73</v>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>Avatco Inc - Camille Lopez de Leon</t>
-        </is>
-      </c>
-      <c r="J49" t="n">
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>3670</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>46155</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G74" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>3671</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G75" t="n">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="H75" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>3672</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G76" t="n">
+        <v>9.74</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>3673</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>3674</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>3675</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G79" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="H79" t="n">
+        <v>-0.97</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>3676</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G80" t="n">
+        <v>8.279999999999999</v>
+      </c>
+      <c r="H80" t="n">
+        <v>-1.22</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>3677</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G81" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="H81" t="n">
+        <v>-5.53</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
         <v>8614</v>
       </c>
     </row>
@@ -2271,13 +3441,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>72</v>
+        <v>124</v>
       </c>
       <c r="C2" t="n">
-        <v>71.5</v>
+        <v>104.7</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.5</v>
+        <v>-19.3</v>
       </c>
     </row>
     <row r="3">
@@ -2287,13 +3457,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>72</v>
+        <v>125</v>
       </c>
       <c r="C3" t="n">
-        <v>71.17999999999999</v>
+        <v>106.44</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.8200000000000001</v>
+        <v>-18.56</v>
       </c>
     </row>
     <row r="4">
@@ -2303,13 +3473,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="C4" t="n">
-        <v>71.37</v>
+        <v>129.08</v>
       </c>
       <c r="D4" t="n">
-        <v>-4.63</v>
+        <v>-3.919999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -2319,13 +3489,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="C5" t="n">
-        <v>62.24</v>
+        <v>116.01</v>
       </c>
       <c r="D5" t="n">
-        <v>-13.76</v>
+        <v>-16.99</v>
       </c>
     </row>
   </sheetData>

--- a/sheet/8614.xlsx
+++ b/sheet/8614.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J81"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,7 +470,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>465</v>
+        <v>124</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>466</v>
+        <v>125</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -540,7 +540,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>467</v>
+        <v>126</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>468</v>
+        <v>127</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -610,7 +610,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>469</v>
+        <v>128</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>470</v>
+        <v>129</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>471</v>
+        <v>130</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>472</v>
+        <v>131</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>473</v>
+        <v>132</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>474</v>
+        <v>133</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>475</v>
+        <v>134</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>476</v>
+        <v>135</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -910,15 +910,15 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>477</v>
+        <v>155</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BERDIN, DENISE G [6595]</t>
+          <t>BERDIN, GILLYZA L [6565]</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>46155</v>
+        <v>46143</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -934,10 +934,10 @@
         <v>9</v>
       </c>
       <c r="G14" t="n">
-        <v>8.82</v>
+        <v>8.92</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.18</v>
+        <v>-0.08</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -950,21 +950,21 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>478</v>
+        <v>156</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BERDIN, DENISE G [6595]</t>
+          <t>BERDIN, GILLYZA L [6565]</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>46156</v>
+        <v>46144</v>
       </c>
       <c r="F15" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -980,21 +980,21 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>479</v>
+        <v>157</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BERDIN, DENISE G [6595]</t>
+          <t>BERDIN, GILLYZA L [6565]</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>46157</v>
+        <v>46145</v>
       </c>
       <c r="F16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1010,24 +1010,34 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>480</v>
+        <v>158</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BERDIN, DENISE G [6595]</t>
+          <t>BERDIN, GILLYZA L [6565]</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>46158</v>
+        <v>46146</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1040,24 +1050,34 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>481</v>
+        <v>159</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BERDIN, DENISE G [6595]</t>
+          <t>BERDIN, GILLYZA L [6565]</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>46159</v>
+        <v>46147</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>8.93</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1070,15 +1090,15 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>482</v>
+        <v>160</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BERDIN, DENISE G [6595]</t>
+          <t>BERDIN, GILLYZA L [6565]</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>46160</v>
+        <v>46148</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1094,10 +1114,10 @@
         <v>9</v>
       </c>
       <c r="G19" t="n">
-        <v>8.380000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.62</v>
+        <v>-0.4</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1110,15 +1130,15 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>483</v>
+        <v>161</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BERDIN, DENISE G [6595]</t>
+          <t>BERDIN, GILLYZA L [6565]</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>46161</v>
+        <v>46149</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1134,10 +1154,10 @@
         <v>9</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>-9</v>
+        <v>-0.13</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1150,15 +1170,15 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>484</v>
+        <v>162</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BERDIN, DENISE G [6595]</t>
+          <t>BERDIN, GILLYZA L [6565]</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>46162</v>
+        <v>46150</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1174,10 +1194,10 @@
         <v>9</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>-9</v>
+        <v>-0.13</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1190,7 +1210,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>496</v>
+        <v>163</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1198,26 +1218,16 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>46143</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46151</v>
       </c>
       <c r="F22" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>8.92</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.08</v>
+        <v>0</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1230,7 +1240,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>497</v>
+        <v>164</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1238,7 +1248,7 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>46144</v>
+        <v>46152</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -1260,7 +1270,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>498</v>
+        <v>165</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1268,16 +1278,26 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>46145</v>
+        <v>46153</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1290,7 +1310,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>499</v>
+        <v>166</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1298,7 +1318,7 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>46146</v>
+        <v>46154</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1314,10 +1334,10 @@
         <v>9</v>
       </c>
       <c r="G25" t="n">
-        <v>8.9</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.1</v>
+        <v>0.14</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1330,19 +1350,19 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>500</v>
+        <v>620</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BERDIN, GILLYZA L [6565]</t>
+          <t>LAO, ZYRA M [1144]</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>46147</v>
+        <v>46143</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1351,13 +1371,13 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="G26" t="n">
-        <v>8.93</v>
+        <v>9.74</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.24</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1370,34 +1390,24 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>501</v>
+        <v>621</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BERDIN, GILLYZA L [6565]</t>
+          <t>LAO, ZYRA M [1144]</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>46148</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46144</v>
       </c>
       <c r="F27" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.4</v>
+        <v>0</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1410,34 +1420,24 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>502</v>
+        <v>622</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BERDIN, GILLYZA L [6565]</t>
+          <t>LAO, ZYRA M [1144]</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>46149</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46145</v>
       </c>
       <c r="F28" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>8.869999999999999</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.13</v>
+        <v>0</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1450,19 +1450,19 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>503</v>
+        <v>623</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BERDIN, GILLYZA L [6565]</t>
+          <t>LAO, ZYRA M [1144]</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>46150</v>
+        <v>46146</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1471,13 +1471,13 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="G29" t="n">
-        <v>8.869999999999999</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.13</v>
+        <v>0.05</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1490,24 +1490,34 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>504</v>
+        <v>624</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BERDIN, GILLYZA L [6565]</t>
+          <t>LAO, ZYRA M [1144]</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>46151</v>
+        <v>46147</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>-4.93</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1520,24 +1530,34 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>505</v>
+        <v>625</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BERDIN, GILLYZA L [6565]</t>
+          <t>LAO, ZYRA M [1144]</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>46152</v>
+        <v>46148</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>-0.45</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1550,19 +1570,19 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>506</v>
+        <v>626</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BERDIN, GILLYZA L [6565]</t>
+          <t>LAO, ZYRA M [1144]</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>46153</v>
+        <v>46149</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1571,13 +1591,13 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="G32" t="n">
-        <v>8.949999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1590,19 +1610,19 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>507</v>
+        <v>627</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BERDIN, GILLYZA L [6565]</t>
+          <t>LAO, ZYRA M [1144]</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>46154</v>
+        <v>46150</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1611,13 +1631,13 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="G33" t="n">
-        <v>9.140000000000001</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="H33" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -1630,34 +1650,24 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>508</v>
+        <v>628</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BERDIN, GILLYZA L [6565]</t>
+          <t>LAO, ZYRA M [1144]</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>46155</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46151</v>
       </c>
       <c r="F34" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>9.050000000000001</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -1670,21 +1680,21 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>509</v>
+        <v>629</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BERDIN, GILLYZA L [6565]</t>
+          <t>LAO, ZYRA M [1144]</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>46156</v>
+        <v>46152</v>
       </c>
       <c r="F35" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1700,19 +1710,19 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>510</v>
+        <v>630</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BERDIN, GILLYZA L [6565]</t>
+          <t>LAO, ZYRA M [1144]</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>46157</v>
+        <v>46153</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1721,13 +1731,13 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="G36" t="n">
-        <v>9.050000000000001</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="H36" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -1740,24 +1750,34 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>511</v>
+        <v>631</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BERDIN, GILLYZA L [6565]</t>
+          <t>LAO, ZYRA M [1144]</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>46158</v>
+        <v>46154</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -1770,24 +1790,34 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>512</v>
+        <v>1240</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BERDIN, GILLYZA L [6565]</t>
+          <t>VILLAROMAN, JAMIE [1164]</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>46159</v>
+        <v>46143</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>6.34</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>-3.16</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -1800,34 +1830,24 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>513</v>
+        <v>1241</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BERDIN, GILLYZA L [6565]</t>
+          <t>VILLAROMAN, JAMIE [1164]</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>46160</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46144</v>
       </c>
       <c r="F39" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>9.16</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -1840,34 +1860,24 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>514</v>
+        <v>1242</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BERDIN, GILLYZA L [6565]</t>
+          <t>VILLAROMAN, JAMIE [1164]</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>46161</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46145</v>
       </c>
       <c r="F40" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-9</v>
+        <v>0</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -1880,15 +1890,15 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>515</v>
+        <v>1243</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BERDIN, GILLYZA L [6565]</t>
+          <t>VILLAROMAN, JAMIE [1164]</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>46162</v>
+        <v>46146</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1897,17 +1907,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>06:30 PM</t>
+          <t>07:00 PM</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>6.67</v>
       </c>
       <c r="H41" t="n">
-        <v>-9</v>
+        <v>-2.83</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -1920,34 +1930,34 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1705</v>
+        <v>1244</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>LAO, ZYRA M [1144]</t>
+          <t>VILLAROMAN, JAMIE [1164]</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>46143</v>
+        <v>46147</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>08:30 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>06:30 PM</t>
+          <t>07:00 PM</t>
         </is>
       </c>
       <c r="F42" t="n">
         <v>9.5</v>
       </c>
       <c r="G42" t="n">
-        <v>9.74</v>
+        <v>8.18</v>
       </c>
       <c r="H42" t="n">
-        <v>0.24</v>
+        <v>-1.32</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -1960,24 +1970,34 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>1706</v>
+        <v>1245</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>LAO, ZYRA M [1144]</t>
+          <t>VILLAROMAN, JAMIE [1164]</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>46144</v>
+        <v>46148</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>-5.12</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -1990,24 +2010,34 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>1707</v>
+        <v>1246</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>LAO, ZYRA M [1144]</t>
+          <t>VILLAROMAN, JAMIE [1164]</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>46145</v>
+        <v>46149</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>-0.7</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2020,34 +2050,34 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1708</v>
+        <v>1247</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>LAO, ZYRA M [1144]</t>
+          <t>VILLAROMAN, JAMIE [1164]</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>46146</v>
+        <v>46150</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>08:30 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>06:30 PM</t>
+          <t>07:00 PM</t>
         </is>
       </c>
       <c r="F45" t="n">
         <v>9.5</v>
       </c>
       <c r="G45" t="n">
-        <v>9.550000000000001</v>
+        <v>8.77</v>
       </c>
       <c r="H45" t="n">
-        <v>0.05</v>
+        <v>-0.73</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2060,34 +2090,24 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1709</v>
+        <v>1248</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>LAO, ZYRA M [1144]</t>
+          <t>VILLAROMAN, JAMIE [1164]</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>46147</v>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>08:30 AM</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46151</v>
       </c>
       <c r="F46" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>9.550000000000001</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2100,34 +2120,24 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1710</v>
+        <v>1249</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>LAO, ZYRA M [1144]</t>
+          <t>VILLAROMAN, JAMIE [1164]</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>46148</v>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>08:30 AM</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46152</v>
       </c>
       <c r="F47" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>9.050000000000001</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.45</v>
+        <v>0</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2140,34 +2150,34 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1711</v>
+        <v>1250</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>LAO, ZYRA M [1144]</t>
+          <t>VILLAROMAN, JAMIE [1164]</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>08:30 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>06:30 PM</t>
+          <t>07:00 PM</t>
         </is>
       </c>
       <c r="F48" t="n">
         <v>9.5</v>
       </c>
       <c r="G48" t="n">
-        <v>9.5</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>-0.63</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2180,34 +2190,34 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1712</v>
+        <v>1251</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>LAO, ZYRA M [1144]</t>
+          <t>VILLAROMAN, JAMIE [1164]</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>46150</v>
+        <v>46154</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>08:30 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>06:30 PM</t>
+          <t>07:00 PM</t>
         </is>
       </c>
       <c r="F49" t="n">
         <v>9.5</v>
       </c>
       <c r="G49" t="n">
-        <v>9.630000000000001</v>
+        <v>10.23</v>
       </c>
       <c r="H49" t="n">
-        <v>0.13</v>
+        <v>0.73</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2215,1186 +2225,6 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>8614</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>1713</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>LAO, ZYRA M [1144]</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="n">
-        <v>46151</v>
-      </c>
-      <c r="F50" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>Avatco Inc - Camille Lopez de Leon</t>
-        </is>
-      </c>
-      <c r="J50" t="n">
-        <v>8614</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>1714</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>LAO, ZYRA M [1144]</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="n">
-        <v>46152</v>
-      </c>
-      <c r="F51" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>Avatco Inc - Camille Lopez de Leon</t>
-        </is>
-      </c>
-      <c r="J51" t="n">
-        <v>8614</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>1715</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>LAO, ZYRA M [1144]</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="n">
-        <v>46153</v>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>08:30 AM</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
-      </c>
-      <c r="F52" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="G52" t="n">
-        <v>9.529999999999999</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>Avatco Inc - Camille Lopez de Leon</t>
-        </is>
-      </c>
-      <c r="J52" t="n">
-        <v>8614</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>1716</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>LAO, ZYRA M [1144]</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="n">
-        <v>46154</v>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>08:30 AM</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
-      </c>
-      <c r="F53" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="G53" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>Avatco Inc - Camille Lopez de Leon</t>
-        </is>
-      </c>
-      <c r="J53" t="n">
-        <v>8614</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>1717</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>LAO, ZYRA M [1144]</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="n">
-        <v>46155</v>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>08:30 AM</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
-      </c>
-      <c r="F54" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="G54" t="n">
-        <v>9.73</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>Avatco Inc - Camille Lopez de Leon</t>
-        </is>
-      </c>
-      <c r="J54" t="n">
-        <v>8614</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>1718</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>LAO, ZYRA M [1144]</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="n">
-        <v>46156</v>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>08:30 AM</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
-      </c>
-      <c r="F55" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="G55" t="n">
-        <v>9.43</v>
-      </c>
-      <c r="H55" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>Avatco Inc - Camille Lopez de Leon</t>
-        </is>
-      </c>
-      <c r="J55" t="n">
-        <v>8614</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>1719</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>LAO, ZYRA M [1144]</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="n">
-        <v>46157</v>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>08:30 AM</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
-      </c>
-      <c r="F56" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="G56" t="n">
-        <v>9.890000000000001</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>Avatco Inc - Camille Lopez de Leon</t>
-        </is>
-      </c>
-      <c r="J56" t="n">
-        <v>8614</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>1720</v>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>LAO, ZYRA M [1144]</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="n">
-        <v>46158</v>
-      </c>
-      <c r="F57" t="n">
-        <v>0</v>
-      </c>
-      <c r="G57" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>Avatco Inc - Camille Lopez de Leon</t>
-        </is>
-      </c>
-      <c r="J57" t="n">
-        <v>8614</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>1721</v>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>LAO, ZYRA M [1144]</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="n">
-        <v>46159</v>
-      </c>
-      <c r="F58" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>Avatco Inc - Camille Lopez de Leon</t>
-        </is>
-      </c>
-      <c r="J58" t="n">
-        <v>8614</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>1722</v>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>LAO, ZYRA M [1144]</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="n">
-        <v>46160</v>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>08:30 AM</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
-      </c>
-      <c r="F59" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="G59" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>Avatco Inc - Camille Lopez de Leon</t>
-        </is>
-      </c>
-      <c r="J59" t="n">
-        <v>8614</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>1723</v>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>LAO, ZYRA M [1144]</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="n">
-        <v>46161</v>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>08:30 AM</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
-      </c>
-      <c r="F60" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="G60" t="n">
-        <v>9.449999999999999</v>
-      </c>
-      <c r="H60" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>Avatco Inc - Camille Lopez de Leon</t>
-        </is>
-      </c>
-      <c r="J60" t="n">
-        <v>8614</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>1724</v>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>LAO, ZYRA M [1144]</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="n">
-        <v>46162</v>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>08:30 AM</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
-      </c>
-      <c r="F61" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="G61" t="n">
-        <v>4.73</v>
-      </c>
-      <c r="H61" t="n">
-        <v>-4.77</v>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>Avatco Inc - Camille Lopez de Leon</t>
-        </is>
-      </c>
-      <c r="J61" t="n">
-        <v>8614</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>3658</v>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="n">
-        <v>46143</v>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>07:00 PM</t>
-        </is>
-      </c>
-      <c r="F62" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="G62" t="n">
-        <v>6.34</v>
-      </c>
-      <c r="H62" t="n">
-        <v>-3.16</v>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>Avatco Inc - Camille Lopez de Leon</t>
-        </is>
-      </c>
-      <c r="J62" t="n">
-        <v>8614</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>3659</v>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="n">
-        <v>46144</v>
-      </c>
-      <c r="F63" t="n">
-        <v>0</v>
-      </c>
-      <c r="G63" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>Avatco Inc - Camille Lopez de Leon</t>
-        </is>
-      </c>
-      <c r="J63" t="n">
-        <v>8614</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>3660</v>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="n">
-        <v>46145</v>
-      </c>
-      <c r="F64" t="n">
-        <v>0</v>
-      </c>
-      <c r="G64" t="n">
-        <v>0</v>
-      </c>
-      <c r="H64" t="n">
-        <v>0</v>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>Avatco Inc - Camille Lopez de Leon</t>
-        </is>
-      </c>
-      <c r="J64" t="n">
-        <v>8614</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>3661</v>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="n">
-        <v>46146</v>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>07:00 PM</t>
-        </is>
-      </c>
-      <c r="F65" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="G65" t="n">
-        <v>6.67</v>
-      </c>
-      <c r="H65" t="n">
-        <v>-2.83</v>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>Avatco Inc - Camille Lopez de Leon</t>
-        </is>
-      </c>
-      <c r="J65" t="n">
-        <v>8614</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>3662</v>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="n">
-        <v>46147</v>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>07:00 PM</t>
-        </is>
-      </c>
-      <c r="F66" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="G66" t="n">
-        <v>8.18</v>
-      </c>
-      <c r="H66" t="n">
-        <v>-1.32</v>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>Avatco Inc - Camille Lopez de Leon</t>
-        </is>
-      </c>
-      <c r="J66" t="n">
-        <v>8614</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>3663</v>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="n">
-        <v>46148</v>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>07:00 PM</t>
-        </is>
-      </c>
-      <c r="F67" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="G67" t="n">
-        <v>8.550000000000001</v>
-      </c>
-      <c r="H67" t="n">
-        <v>-0.95</v>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>Avatco Inc - Camille Lopez de Leon</t>
-        </is>
-      </c>
-      <c r="J67" t="n">
-        <v>8614</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>3664</v>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="n">
-        <v>46149</v>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>07:00 PM</t>
-        </is>
-      </c>
-      <c r="F68" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="G68" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="H68" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>Avatco Inc - Camille Lopez de Leon</t>
-        </is>
-      </c>
-      <c r="J68" t="n">
-        <v>8614</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>3665</v>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="n">
-        <v>46150</v>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>07:00 PM</t>
-        </is>
-      </c>
-      <c r="F69" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="G69" t="n">
-        <v>8.77</v>
-      </c>
-      <c r="H69" t="n">
-        <v>-0.73</v>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>Avatco Inc - Camille Lopez de Leon</t>
-        </is>
-      </c>
-      <c r="J69" t="n">
-        <v>8614</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>3666</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="n">
-        <v>46151</v>
-      </c>
-      <c r="F70" t="n">
-        <v>0</v>
-      </c>
-      <c r="G70" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>Avatco Inc - Camille Lopez de Leon</t>
-        </is>
-      </c>
-      <c r="J70" t="n">
-        <v>8614</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>3667</v>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="n">
-        <v>46152</v>
-      </c>
-      <c r="F71" t="n">
-        <v>0</v>
-      </c>
-      <c r="G71" t="n">
-        <v>0</v>
-      </c>
-      <c r="H71" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>Avatco Inc - Camille Lopez de Leon</t>
-        </is>
-      </c>
-      <c r="J71" t="n">
-        <v>8614</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>3668</v>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="n">
-        <v>46153</v>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>07:00 PM</t>
-        </is>
-      </c>
-      <c r="F72" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="G72" t="n">
-        <v>8.869999999999999</v>
-      </c>
-      <c r="H72" t="n">
-        <v>-0.63</v>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>Avatco Inc - Camille Lopez de Leon</t>
-        </is>
-      </c>
-      <c r="J72" t="n">
-        <v>8614</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>3669</v>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="n">
-        <v>46154</v>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>07:00 PM</t>
-        </is>
-      </c>
-      <c r="F73" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="G73" t="n">
-        <v>10.23</v>
-      </c>
-      <c r="H73" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>Avatco Inc - Camille Lopez de Leon</t>
-        </is>
-      </c>
-      <c r="J73" t="n">
-        <v>8614</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>3670</v>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="n">
-        <v>46155</v>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>07:00 PM</t>
-        </is>
-      </c>
-      <c r="F74" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="G74" t="n">
-        <v>9.630000000000001</v>
-      </c>
-      <c r="H74" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>Avatco Inc - Camille Lopez de Leon</t>
-        </is>
-      </c>
-      <c r="J74" t="n">
-        <v>8614</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>3671</v>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="n">
-        <v>46156</v>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>07:00 PM</t>
-        </is>
-      </c>
-      <c r="F75" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="G75" t="n">
-        <v>9.449999999999999</v>
-      </c>
-      <c r="H75" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>Avatco Inc - Camille Lopez de Leon</t>
-        </is>
-      </c>
-      <c r="J75" t="n">
-        <v>8614</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>3672</v>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="n">
-        <v>46157</v>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>07:00 PM</t>
-        </is>
-      </c>
-      <c r="F76" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="G76" t="n">
-        <v>9.74</v>
-      </c>
-      <c r="H76" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>Avatco Inc - Camille Lopez de Leon</t>
-        </is>
-      </c>
-      <c r="J76" t="n">
-        <v>8614</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="n">
-        <v>3673</v>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="n">
-        <v>46158</v>
-      </c>
-      <c r="F77" t="n">
-        <v>0</v>
-      </c>
-      <c r="G77" t="n">
-        <v>0</v>
-      </c>
-      <c r="H77" t="n">
-        <v>0</v>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>Avatco Inc - Camille Lopez de Leon</t>
-        </is>
-      </c>
-      <c r="J77" t="n">
-        <v>8614</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
-        <v>3674</v>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="n">
-        <v>46159</v>
-      </c>
-      <c r="F78" t="n">
-        <v>0</v>
-      </c>
-      <c r="G78" t="n">
-        <v>0</v>
-      </c>
-      <c r="H78" t="n">
-        <v>0</v>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>Avatco Inc - Camille Lopez de Leon</t>
-        </is>
-      </c>
-      <c r="J78" t="n">
-        <v>8614</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="n">
-        <v>3675</v>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="n">
-        <v>46160</v>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>07:00 PM</t>
-        </is>
-      </c>
-      <c r="F79" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="G79" t="n">
-        <v>8.529999999999999</v>
-      </c>
-      <c r="H79" t="n">
-        <v>-0.97</v>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>Avatco Inc - Camille Lopez de Leon</t>
-        </is>
-      </c>
-      <c r="J79" t="n">
-        <v>8614</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
-        <v>3676</v>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="n">
-        <v>46161</v>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>07:00 PM</t>
-        </is>
-      </c>
-      <c r="F80" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="G80" t="n">
-        <v>8.279999999999999</v>
-      </c>
-      <c r="H80" t="n">
-        <v>-1.22</v>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>Avatco Inc - Camille Lopez de Leon</t>
-        </is>
-      </c>
-      <c r="J80" t="n">
-        <v>8614</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>3677</v>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="n">
-        <v>46162</v>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>07:00 PM</t>
-        </is>
-      </c>
-      <c r="F81" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="G81" t="n">
-        <v>3.97</v>
-      </c>
-      <c r="H81" t="n">
-        <v>-5.53</v>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>Avatco Inc - Camille Lopez de Leon</t>
-        </is>
-      </c>
-      <c r="J81" t="n">
         <v>8614</v>
       </c>
     </row>
@@ -3441,13 +2271,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>124</v>
+        <v>72</v>
       </c>
       <c r="C2" t="n">
-        <v>104.7</v>
+        <v>71.5</v>
       </c>
       <c r="D2" t="n">
-        <v>-19.3</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="3">
@@ -3457,13 +2287,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>125</v>
+        <v>72</v>
       </c>
       <c r="C3" t="n">
-        <v>106.44</v>
+        <v>71.17999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>-18.56</v>
+        <v>-0.8200000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -3473,13 +2303,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>133</v>
+        <v>76</v>
       </c>
       <c r="C4" t="n">
-        <v>129.08</v>
+        <v>71.37</v>
       </c>
       <c r="D4" t="n">
-        <v>-3.919999999999999</v>
+        <v>-4.63</v>
       </c>
     </row>
     <row r="5">
@@ -3489,13 +2319,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>133</v>
+        <v>76</v>
       </c>
       <c r="C5" t="n">
-        <v>116.01</v>
+        <v>62.24</v>
       </c>
       <c r="D5" t="n">
-        <v>-16.99</v>
+        <v>-13.76</v>
       </c>
     </row>
   </sheetData>

--- a/sheet/8614.xlsx
+++ b/sheet/8614.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:J81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,7 +470,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124</v>
+        <v>465</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125</v>
+        <v>466</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -540,7 +540,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126</v>
+        <v>467</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127</v>
+        <v>468</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -610,7 +610,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128</v>
+        <v>469</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129</v>
+        <v>470</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130</v>
+        <v>471</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131</v>
+        <v>472</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132</v>
+        <v>473</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133</v>
+        <v>474</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134</v>
+        <v>475</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135</v>
+        <v>476</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -910,15 +910,15 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>155</v>
+        <v>477</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BERDIN, GILLYZA L [6565]</t>
+          <t>BERDIN, DENISE G [6595]</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>46143</v>
+        <v>46155</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -934,10 +934,10 @@
         <v>9</v>
       </c>
       <c r="G14" t="n">
-        <v>8.92</v>
+        <v>8.82</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.08</v>
+        <v>-0.18</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -950,21 +950,21 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>156</v>
+        <v>478</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BERDIN, GILLYZA L [6565]</t>
+          <t>BERDIN, DENISE G [6595]</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>46144</v>
+        <v>46156</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -980,21 +980,21 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>157</v>
+        <v>479</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BERDIN, GILLYZA L [6565]</t>
+          <t>BERDIN, DENISE G [6595]</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>46145</v>
+        <v>46157</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1010,34 +1010,24 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>158</v>
+        <v>480</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BERDIN, GILLYZA L [6565]</t>
+          <t>BERDIN, DENISE G [6595]</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>46146</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46158</v>
       </c>
       <c r="F17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1050,34 +1040,24 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>159</v>
+        <v>481</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BERDIN, GILLYZA L [6565]</t>
+          <t>BERDIN, DENISE G [6595]</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>46147</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46159</v>
       </c>
       <c r="F18" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>8.93</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1090,15 +1070,15 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>160</v>
+        <v>482</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BERDIN, GILLYZA L [6565]</t>
+          <t>BERDIN, DENISE G [6595]</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>46148</v>
+        <v>46160</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1114,10 +1094,10 @@
         <v>9</v>
       </c>
       <c r="G19" t="n">
-        <v>8.6</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4</v>
+        <v>-0.62</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1130,15 +1110,15 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>161</v>
+        <v>483</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BERDIN, GILLYZA L [6565]</t>
+          <t>BERDIN, DENISE G [6595]</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>46149</v>
+        <v>46161</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1154,10 +1134,10 @@
         <v>9</v>
       </c>
       <c r="G20" t="n">
-        <v>8.869999999999999</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.13</v>
+        <v>-9</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1170,15 +1150,15 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>162</v>
+        <v>484</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BERDIN, GILLYZA L [6565]</t>
+          <t>BERDIN, DENISE G [6595]</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>46150</v>
+        <v>46162</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1194,10 +1174,10 @@
         <v>9</v>
       </c>
       <c r="G21" t="n">
-        <v>8.869999999999999</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.13</v>
+        <v>-9</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1210,7 +1190,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>163</v>
+        <v>496</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1218,16 +1198,26 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>46151</v>
+        <v>46143</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>8.92</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1240,7 +1230,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>164</v>
+        <v>497</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1248,7 +1238,7 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>46152</v>
+        <v>46144</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -1270,7 +1260,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>165</v>
+        <v>498</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1278,26 +1268,16 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>46153</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46145</v>
       </c>
       <c r="F24" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>8.949999999999999</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1310,7 +1290,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>166</v>
+        <v>499</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1318,7 +1298,7 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>46154</v>
+        <v>46146</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1334,10 +1314,10 @@
         <v>9</v>
       </c>
       <c r="G25" t="n">
-        <v>9.140000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="H25" t="n">
-        <v>0.14</v>
+        <v>-0.1</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1350,19 +1330,19 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>620</v>
+        <v>500</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LAO, ZYRA M [1144]</t>
+          <t>BERDIN, GILLYZA L [6565]</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>46143</v>
+        <v>46147</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>08:30 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1371,13 +1351,13 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="G26" t="n">
-        <v>9.74</v>
+        <v>8.93</v>
       </c>
       <c r="H26" t="n">
-        <v>0.24</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1390,24 +1370,34 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>621</v>
+        <v>501</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LAO, ZYRA M [1144]</t>
+          <t>BERDIN, GILLYZA L [6565]</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>46144</v>
+        <v>46148</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1420,24 +1410,34 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>622</v>
+        <v>502</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>LAO, ZYRA M [1144]</t>
+          <t>BERDIN, GILLYZA L [6565]</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>46145</v>
+        <v>46149</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>-0.13</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1450,19 +1450,19 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>623</v>
+        <v>503</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>LAO, ZYRA M [1144]</t>
+          <t>BERDIN, GILLYZA L [6565]</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>46146</v>
+        <v>46150</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>08:30 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1471,13 +1471,13 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="G29" t="n">
-        <v>9.550000000000001</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="H29" t="n">
-        <v>0.05</v>
+        <v>-0.13</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1490,34 +1490,24 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>624</v>
+        <v>504</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>LAO, ZYRA M [1144]</t>
+          <t>BERDIN, GILLYZA L [6565]</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>46147</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>08:30 AM</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46151</v>
       </c>
       <c r="F30" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-4.93</v>
+        <v>0</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1530,34 +1520,24 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>625</v>
+        <v>505</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>LAO, ZYRA M [1144]</t>
+          <t>BERDIN, GILLYZA L [6565]</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>46148</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>08:30 AM</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46152</v>
       </c>
       <c r="F31" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>9.050000000000001</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.45</v>
+        <v>0</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1570,19 +1550,19 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>626</v>
+        <v>506</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>LAO, ZYRA M [1144]</t>
+          <t>BERDIN, GILLYZA L [6565]</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>08:30 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1591,13 +1571,13 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="G32" t="n">
-        <v>9.5</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1610,19 +1590,19 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>627</v>
+        <v>507</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>LAO, ZYRA M [1144]</t>
+          <t>BERDIN, GILLYZA L [6565]</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>46150</v>
+        <v>46154</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>08:30 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1631,13 +1611,13 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="G33" t="n">
-        <v>9.630000000000001</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="H33" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -1650,24 +1630,34 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>628</v>
+        <v>508</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>LAO, ZYRA M [1144]</t>
+          <t>BERDIN, GILLYZA L [6565]</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>46151</v>
+        <v>46155</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -1680,21 +1670,21 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>629</v>
+        <v>509</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>LAO, ZYRA M [1144]</t>
+          <t>BERDIN, GILLYZA L [6565]</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>46152</v>
+        <v>46156</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1710,19 +1700,19 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>630</v>
+        <v>510</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>LAO, ZYRA M [1144]</t>
+          <t>BERDIN, GILLYZA L [6565]</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>46153</v>
+        <v>46157</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>08:30 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1731,13 +1721,13 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="G36" t="n">
-        <v>9.529999999999999</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="H36" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -1750,34 +1740,24 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>631</v>
+        <v>511</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>LAO, ZYRA M [1144]</t>
+          <t>BERDIN, GILLYZA L [6565]</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>46154</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>08:30 AM</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46158</v>
       </c>
       <c r="F37" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -1790,34 +1770,24 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1240</v>
+        <v>512</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
+          <t>BERDIN, GILLYZA L [6565]</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>46143</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>07:00 PM</t>
-        </is>
+        <v>46159</v>
       </c>
       <c r="F38" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>6.34</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-3.16</v>
+        <v>0</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -1830,24 +1800,34 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1241</v>
+        <v>513</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
+          <t>BERDIN, GILLYZA L [6565]</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>46144</v>
+        <v>46160</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>9.16</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -1860,24 +1840,34 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1242</v>
+        <v>514</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
+          <t>BERDIN, GILLYZA L [6565]</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>46145</v>
+        <v>46161</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -1890,15 +1880,15 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1243</v>
+        <v>515</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
+          <t>BERDIN, GILLYZA L [6565]</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>46146</v>
+        <v>46162</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1907,17 +1897,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>07:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="G41" t="n">
-        <v>6.67</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.83</v>
+        <v>-9</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -1930,34 +1920,34 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1244</v>
+        <v>1705</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
+          <t>LAO, ZYRA M [1144]</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>46147</v>
+        <v>46143</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>07:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F42" t="n">
         <v>9.5</v>
       </c>
       <c r="G42" t="n">
-        <v>8.18</v>
+        <v>9.74</v>
       </c>
       <c r="H42" t="n">
-        <v>-1.32</v>
+        <v>0.24</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -1970,34 +1960,24 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>1245</v>
+        <v>1706</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
+          <t>LAO, ZYRA M [1144]</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>46148</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>07:00 PM</t>
-        </is>
+        <v>46144</v>
       </c>
       <c r="F43" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>-5.12</v>
+        <v>0</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2010,34 +1990,24 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>1246</v>
+        <v>1707</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
+          <t>LAO, ZYRA M [1144]</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>46149</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>07:00 PM</t>
-        </is>
+        <v>46145</v>
       </c>
       <c r="F44" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.7</v>
+        <v>0</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2050,34 +2020,34 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1247</v>
+        <v>1708</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
+          <t>LAO, ZYRA M [1144]</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>46150</v>
+        <v>46146</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>07:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F45" t="n">
         <v>9.5</v>
       </c>
       <c r="G45" t="n">
-        <v>8.77</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.73</v>
+        <v>0.05</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2090,24 +2060,34 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1248</v>
+        <v>1709</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
+          <t>LAO, ZYRA M [1144]</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>46151</v>
+        <v>46147</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2120,24 +2100,34 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1249</v>
+        <v>1710</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
+          <t>LAO, ZYRA M [1144]</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>46152</v>
+        <v>46148</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>-0.45</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2150,34 +2140,34 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1250</v>
+        <v>1711</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
+          <t>LAO, ZYRA M [1144]</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>46153</v>
+        <v>46149</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>07:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F48" t="n">
         <v>9.5</v>
       </c>
       <c r="G48" t="n">
-        <v>8.869999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.63</v>
+        <v>0</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2190,41 +2180,1221 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1251</v>
+        <v>1712</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
+          <t>LAO, ZYRA M [1144]</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>46154</v>
+        <v>46150</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>07:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F49" t="n">
         <v>9.5</v>
       </c>
       <c r="G49" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>1713</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>LAO, ZYRA M [1144]</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>1714</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>LAO, ZYRA M [1144]</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>1715</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>LAO, ZYRA M [1144]</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G52" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>1716</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>LAO, ZYRA M [1144]</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G53" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>1717</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>LAO, ZYRA M [1144]</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>46155</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G54" t="n">
+        <v>9.73</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>1718</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>LAO, ZYRA M [1144]</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G55" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="H55" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>1719</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>LAO, ZYRA M [1144]</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G56" t="n">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>1720</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>LAO, ZYRA M [1144]</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>1721</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>LAO, ZYRA M [1144]</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>1722</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>LAO, ZYRA M [1144]</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G59" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>1723</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>LAO, ZYRA M [1144]</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G60" t="n">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="H60" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>1724</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>LAO, ZYRA M [1144]</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G61" t="n">
+        <v>9.41</v>
+      </c>
+      <c r="H61" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>3658</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G62" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="H62" t="n">
+        <v>-3.16</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>3659</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>3660</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>3661</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G65" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="H65" t="n">
+        <v>-2.83</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>3662</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G66" t="n">
+        <v>8.18</v>
+      </c>
+      <c r="H66" t="n">
+        <v>-1.32</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>3663</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G67" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="H67" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>3664</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G68" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="H68" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>3665</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G69" t="n">
+        <v>8.77</v>
+      </c>
+      <c r="H69" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>3666</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>3667</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>3668</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G72" t="n">
+        <v>8.869999999999999</v>
+      </c>
+      <c r="H72" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>3669</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G73" t="n">
         <v>10.23</v>
       </c>
-      <c r="H49" t="n">
+      <c r="H73" t="n">
         <v>0.73</v>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>Avatco Inc - Camille Lopez de Leon</t>
-        </is>
-      </c>
-      <c r="J49" t="n">
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>3670</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>46155</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G74" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>3671</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G75" t="n">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="H75" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>3672</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G76" t="n">
+        <v>9.74</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>3673</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>3674</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>3675</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G79" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="H79" t="n">
+        <v>-0.97</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>3676</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G80" t="n">
+        <v>8.279999999999999</v>
+      </c>
+      <c r="H80" t="n">
+        <v>-1.22</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>3677</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G81" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="H81" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
         <v>8614</v>
       </c>
     </row>
@@ -2271,13 +3441,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>72</v>
+        <v>124</v>
       </c>
       <c r="C2" t="n">
-        <v>71.5</v>
+        <v>104.7</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.5</v>
+        <v>-19.3</v>
       </c>
     </row>
     <row r="3">
@@ -2287,13 +3457,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>72</v>
+        <v>125</v>
       </c>
       <c r="C3" t="n">
-        <v>71.17999999999999</v>
+        <v>106.44</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.8200000000000001</v>
+        <v>-18.56</v>
       </c>
     </row>
     <row r="4">
@@ -2303,13 +3473,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="C4" t="n">
-        <v>71.37</v>
+        <v>133.76</v>
       </c>
       <c r="D4" t="n">
-        <v>-4.63</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="5">
@@ -2319,13 +3489,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="C5" t="n">
-        <v>62.24</v>
+        <v>120.59</v>
       </c>
       <c r="D5" t="n">
-        <v>-13.76</v>
+        <v>-12.41</v>
       </c>
     </row>
   </sheetData>

--- a/sheet/8614.xlsx
+++ b/sheet/8614.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J81"/>
+  <dimension ref="A1:J85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1190,15 +1190,15 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>496</v>
+        <v>485</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BERDIN, GILLYZA L [6565]</t>
+          <t>BERDIN, DENISE G [6595]</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>46143</v>
+        <v>46163</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1214,10 +1214,10 @@
         <v>9</v>
       </c>
       <c r="G22" t="n">
-        <v>8.92</v>
+        <v>4.38</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.08</v>
+        <v>-4.62</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1238,16 +1238,26 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>46144</v>
+        <v>46143</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>8.92</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1260,7 +1270,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1268,7 +1278,7 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>46145</v>
+        <v>46144</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -1290,7 +1300,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1298,26 +1308,16 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>46146</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46145</v>
       </c>
       <c r="F25" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>46147</v>
+        <v>46146</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1354,10 +1354,10 @@
         <v>9</v>
       </c>
       <c r="G26" t="n">
-        <v>8.93</v>
+        <v>8.9</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.1</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>46148</v>
+        <v>46147</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1394,10 +1394,10 @@
         <v>9</v>
       </c>
       <c r="G27" t="n">
-        <v>8.6</v>
+        <v>8.93</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.4</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>46149</v>
+        <v>46148</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1434,10 +1434,10 @@
         <v>9</v>
       </c>
       <c r="G28" t="n">
-        <v>8.869999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.13</v>
+        <v>-0.4</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>46150</v>
+        <v>46149</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1498,16 +1498,26 @@
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>46151</v>
+        <v>46150</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>-0.13</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1520,7 +1530,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1528,7 +1538,7 @@
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>46152</v>
+        <v>46151</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -1550,7 +1560,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1558,26 +1568,16 @@
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>46153</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46152</v>
       </c>
       <c r="F32" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>8.949999999999999</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>46154</v>
+        <v>46153</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1614,10 +1614,10 @@
         <v>9</v>
       </c>
       <c r="G33" t="n">
-        <v>9.140000000000001</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="H33" t="n">
-        <v>0.14</v>
+        <v>-0.05</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>46155</v>
+        <v>46154</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1654,10 +1654,10 @@
         <v>9</v>
       </c>
       <c r="G34" t="n">
-        <v>9.050000000000001</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="H34" t="n">
-        <v>0.05</v>
+        <v>0.14</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1678,16 +1678,26 @@
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>46156</v>
+        <v>46155</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F35" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G35" t="n">
-        <v>8</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -1700,7 +1710,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1708,26 +1718,16 @@
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>46157</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46156</v>
       </c>
       <c r="F36" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G36" t="n">
-        <v>9.050000000000001</v>
+        <v>8</v>
       </c>
       <c r="H36" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1748,16 +1748,26 @@
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>46158</v>
+        <v>46157</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -1770,7 +1780,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -1778,7 +1788,7 @@
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>46159</v>
+        <v>46158</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -1800,7 +1810,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -1808,26 +1818,16 @@
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>46160</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46159</v>
       </c>
       <c r="F39" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>9.16</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>46161</v>
+        <v>46160</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1864,10 +1864,10 @@
         <v>9</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>9.16</v>
       </c>
       <c r="H40" t="n">
-        <v>-9</v>
+        <v>0.16</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>46162</v>
+        <v>46161</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1920,19 +1920,19 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1705</v>
+        <v>515</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>LAO, ZYRA M [1144]</t>
+          <t>BERDIN, GILLYZA L [6565]</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>46143</v>
+        <v>46162</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>08:30 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1941,13 +1941,13 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="G42" t="n">
-        <v>9.74</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.24</v>
+        <v>-9</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -1960,24 +1960,34 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>1706</v>
+        <v>516</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>LAO, ZYRA M [1144]</t>
+          <t>BERDIN, GILLYZA L [6565]</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>46144</v>
+        <v>46163</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>-6.02</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -1990,7 +2000,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>1707</v>
+        <v>1705</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -1998,16 +2008,26 @@
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>46145</v>
+        <v>46143</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>9.74</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2020,7 +2040,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1708</v>
+        <v>1706</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -2028,26 +2048,16 @@
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>46146</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>08:30 AM</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46144</v>
       </c>
       <c r="F45" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>9.550000000000001</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2060,7 +2070,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1709</v>
+        <v>1707</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -2068,26 +2078,16 @@
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>46147</v>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>08:30 AM</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46145</v>
       </c>
       <c r="F46" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>9.550000000000001</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1710</v>
+        <v>1708</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>46148</v>
+        <v>46146</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -2124,10 +2124,10 @@
         <v>9.5</v>
       </c>
       <c r="G47" t="n">
-        <v>9.050000000000001</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.45</v>
+        <v>0.05</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1711</v>
+        <v>1709</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>46149</v>
+        <v>46147</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -2164,10 +2164,10 @@
         <v>9.5</v>
       </c>
       <c r="G48" t="n">
-        <v>9.5</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1712</v>
+        <v>1710</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>46150</v>
+        <v>46148</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2204,10 +2204,10 @@
         <v>9.5</v>
       </c>
       <c r="G49" t="n">
-        <v>9.630000000000001</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="H49" t="n">
-        <v>0.13</v>
+        <v>-0.45</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1713</v>
+        <v>1711</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -2228,13 +2228,23 @@
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>46151</v>
+        <v>46149</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -2250,7 +2260,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1714</v>
+        <v>1712</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -2258,16 +2268,26 @@
         </is>
       </c>
       <c r="C51" s="2" t="n">
-        <v>46152</v>
+        <v>46150</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -2280,7 +2300,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1715</v>
+        <v>1713</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -2288,26 +2308,16 @@
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>46153</v>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>08:30 AM</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46151</v>
       </c>
       <c r="F52" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>9.529999999999999</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -2320,7 +2330,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1716</v>
+        <v>1714</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -2328,26 +2338,16 @@
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>46154</v>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>08:30 AM</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46152</v>
       </c>
       <c r="F53" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>1717</v>
+        <v>1715</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>46155</v>
+        <v>46153</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -2384,10 +2384,10 @@
         <v>9.5</v>
       </c>
       <c r="G54" t="n">
-        <v>9.73</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="H54" t="n">
-        <v>0.23</v>
+        <v>0.03</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>1718</v>
+        <v>1716</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
         </is>
       </c>
       <c r="C55" s="2" t="n">
-        <v>46156</v>
+        <v>46154</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -2424,10 +2424,10 @@
         <v>9.5</v>
       </c>
       <c r="G55" t="n">
-        <v>9.43</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>1719</v>
+        <v>1717</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>46157</v>
+        <v>46155</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -2464,10 +2464,10 @@
         <v>9.5</v>
       </c>
       <c r="G56" t="n">
-        <v>9.890000000000001</v>
+        <v>9.73</v>
       </c>
       <c r="H56" t="n">
-        <v>0.39</v>
+        <v>0.23</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>1720</v>
+        <v>1718</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -2488,16 +2488,26 @@
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>46158</v>
+        <v>46156</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>9.43</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -2510,7 +2520,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>1721</v>
+        <v>1719</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -2518,16 +2528,26 @@
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>46159</v>
+        <v>46157</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>0.39</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -2540,7 +2560,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>1722</v>
+        <v>1720</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -2548,23 +2568,13 @@
         </is>
       </c>
       <c r="C59" s="2" t="n">
-        <v>46160</v>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>08:30 AM</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46158</v>
       </c>
       <c r="F59" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -2580,7 +2590,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>1723</v>
+        <v>1721</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -2588,26 +2598,16 @@
         </is>
       </c>
       <c r="C60" s="2" t="n">
-        <v>46161</v>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>08:30 AM</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46159</v>
       </c>
       <c r="F60" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>9.449999999999999</v>
+        <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>1724</v>
+        <v>1722</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         </is>
       </c>
       <c r="C61" s="2" t="n">
-        <v>46162</v>
+        <v>46160</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -2644,10 +2644,10 @@
         <v>9.5</v>
       </c>
       <c r="G61" t="n">
-        <v>9.41</v>
+        <v>9.5</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.09</v>
+        <v>0</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -2660,34 +2660,34 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>3658</v>
+        <v>1723</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
+          <t>LAO, ZYRA M [1144]</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
-        <v>46143</v>
+        <v>46161</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>07:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F62" t="n">
         <v>9.5</v>
       </c>
       <c r="G62" t="n">
-        <v>6.34</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="H62" t="n">
-        <v>-3.16</v>
+        <v>-0.05</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -2700,24 +2700,34 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>3659</v>
+        <v>1724</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
+          <t>LAO, ZYRA M [1144]</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
-        <v>46144</v>
+        <v>46162</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>9.41</v>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -2730,24 +2740,34 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>3660</v>
+        <v>1725</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
+          <t>LAO, ZYRA M [1144]</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
-        <v>46145</v>
+        <v>46163</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>-4.8</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -2760,7 +2780,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>3661</v>
+        <v>3658</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -2768,7 +2788,7 @@
         </is>
       </c>
       <c r="C65" s="2" t="n">
-        <v>46146</v>
+        <v>46143</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -2784,10 +2804,10 @@
         <v>9.5</v>
       </c>
       <c r="G65" t="n">
-        <v>6.67</v>
+        <v>6.34</v>
       </c>
       <c r="H65" t="n">
-        <v>-2.83</v>
+        <v>-3.16</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -2800,7 +2820,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>3662</v>
+        <v>3659</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -2808,26 +2828,16 @@
         </is>
       </c>
       <c r="C66" s="2" t="n">
-        <v>46147</v>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>07:00 PM</t>
-        </is>
+        <v>46144</v>
       </c>
       <c r="F66" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>8.18</v>
+        <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-1.32</v>
+        <v>0</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -2840,7 +2850,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>3663</v>
+        <v>3660</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -2848,26 +2858,16 @@
         </is>
       </c>
       <c r="C67" s="2" t="n">
-        <v>46148</v>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>07:00 PM</t>
-        </is>
+        <v>46145</v>
       </c>
       <c r="F67" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>8.550000000000001</v>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.95</v>
+        <v>0</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>3664</v>
+        <v>3661</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         </is>
       </c>
       <c r="C68" s="2" t="n">
-        <v>46149</v>
+        <v>46146</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -2904,10 +2904,10 @@
         <v>9.5</v>
       </c>
       <c r="G68" t="n">
-        <v>8.800000000000001</v>
+        <v>6.67</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.7</v>
+        <v>-2.83</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>3665</v>
+        <v>3662</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         </is>
       </c>
       <c r="C69" s="2" t="n">
-        <v>46150</v>
+        <v>46147</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -2944,10 +2944,10 @@
         <v>9.5</v>
       </c>
       <c r="G69" t="n">
-        <v>8.77</v>
+        <v>8.18</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.73</v>
+        <v>-1.32</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>3666</v>
+        <v>3663</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -2968,16 +2968,26 @@
         </is>
       </c>
       <c r="C70" s="2" t="n">
-        <v>46151</v>
+        <v>46148</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
       </c>
       <c r="F70" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>-0.95</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -2990,7 +3000,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>3667</v>
+        <v>3664</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -2998,16 +3008,26 @@
         </is>
       </c>
       <c r="C71" s="2" t="n">
-        <v>46152</v>
+        <v>46149</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
       </c>
       <c r="F71" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H71" t="n">
-        <v>0</v>
+        <v>-0.7</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -3020,7 +3040,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>3668</v>
+        <v>3665</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -3028,7 +3048,7 @@
         </is>
       </c>
       <c r="C72" s="2" t="n">
-        <v>46153</v>
+        <v>46150</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -3044,10 +3064,10 @@
         <v>9.5</v>
       </c>
       <c r="G72" t="n">
-        <v>8.869999999999999</v>
+        <v>8.77</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.63</v>
+        <v>-0.73</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -3060,7 +3080,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>3669</v>
+        <v>3666</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -3068,26 +3088,16 @@
         </is>
       </c>
       <c r="C73" s="2" t="n">
-        <v>46154</v>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>07:00 PM</t>
-        </is>
+        <v>46151</v>
       </c>
       <c r="F73" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>10.23</v>
+        <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>0.73</v>
+        <v>0</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -3100,7 +3110,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>3670</v>
+        <v>3667</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -3108,26 +3118,16 @@
         </is>
       </c>
       <c r="C74" s="2" t="n">
-        <v>46155</v>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>07:00 PM</t>
-        </is>
+        <v>46152</v>
       </c>
       <c r="F74" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>9.630000000000001</v>
+        <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>3671</v>
+        <v>3668</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         </is>
       </c>
       <c r="C75" s="2" t="n">
-        <v>46156</v>
+        <v>46153</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -3164,10 +3164,10 @@
         <v>9.5</v>
       </c>
       <c r="G75" t="n">
-        <v>9.449999999999999</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="H75" t="n">
-        <v>-0.05</v>
+        <v>-0.63</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>3672</v>
+        <v>3669</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         </is>
       </c>
       <c r="C76" s="2" t="n">
-        <v>46157</v>
+        <v>46154</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -3204,10 +3204,10 @@
         <v>9.5</v>
       </c>
       <c r="G76" t="n">
-        <v>9.74</v>
+        <v>10.23</v>
       </c>
       <c r="H76" t="n">
-        <v>0.24</v>
+        <v>0.73</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>3673</v>
+        <v>3670</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -3228,16 +3228,26 @@
         </is>
       </c>
       <c r="C77" s="2" t="n">
-        <v>46158</v>
+        <v>46155</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
       </c>
       <c r="F77" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="H77" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -3250,7 +3260,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>3674</v>
+        <v>3671</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -3258,16 +3268,26 @@
         </is>
       </c>
       <c r="C78" s="2" t="n">
-        <v>46159</v>
+        <v>46156</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
       </c>
       <c r="F78" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="H78" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -3280,7 +3300,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>3675</v>
+        <v>3672</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -3288,7 +3308,7 @@
         </is>
       </c>
       <c r="C79" s="2" t="n">
-        <v>46160</v>
+        <v>46157</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -3304,10 +3324,10 @@
         <v>9.5</v>
       </c>
       <c r="G79" t="n">
-        <v>8.529999999999999</v>
+        <v>9.74</v>
       </c>
       <c r="H79" t="n">
-        <v>-0.97</v>
+        <v>0.24</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -3320,7 +3340,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>3676</v>
+        <v>3673</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -3328,26 +3348,16 @@
         </is>
       </c>
       <c r="C80" s="2" t="n">
-        <v>46161</v>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>07:00 PM</t>
-        </is>
+        <v>46158</v>
       </c>
       <c r="F80" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>8.279999999999999</v>
+        <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>-1.22</v>
+        <v>0</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -3360,41 +3370,191 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
+        <v>3674</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>3675</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G82" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="H82" t="n">
+        <v>-0.97</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>3676</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G83" t="n">
+        <v>8.279999999999999</v>
+      </c>
+      <c r="H83" t="n">
+        <v>-1.22</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
         <v>3677</v>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B84" t="inlineStr">
         <is>
           <t>VILLAROMAN, JAMIE [1164]</t>
         </is>
       </c>
-      <c r="C81" s="2" t="n">
+      <c r="C84" s="2" t="n">
         <v>46162</v>
       </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
         <is>
           <t>07:00 PM</t>
         </is>
       </c>
-      <c r="F81" t="n">
+      <c r="F84" t="n">
         <v>9.5</v>
       </c>
-      <c r="G81" t="n">
+      <c r="G84" t="n">
         <v>8.550000000000001</v>
       </c>
-      <c r="H81" t="n">
+      <c r="H84" t="n">
         <v>-0.95</v>
       </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>Avatco Inc - Camille Lopez de Leon</t>
-        </is>
-      </c>
-      <c r="J81" t="n">
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>3678</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G85" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="H85" t="n">
+        <v>-4.55</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
         <v>8614</v>
       </c>
     </row>
@@ -3441,13 +3601,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="C2" t="n">
-        <v>104.7</v>
+        <v>109.08</v>
       </c>
       <c r="D2" t="n">
-        <v>-19.3</v>
+        <v>-23.92</v>
       </c>
     </row>
     <row r="3">
@@ -3457,13 +3617,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="C3" t="n">
-        <v>106.44</v>
+        <v>109.42</v>
       </c>
       <c r="D3" t="n">
-        <v>-18.56</v>
+        <v>-24.58</v>
       </c>
     </row>
     <row r="4">
@@ -3473,13 +3633,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>133</v>
+        <v>142.5</v>
       </c>
       <c r="C4" t="n">
-        <v>133.76</v>
+        <v>138.46</v>
       </c>
       <c r="D4" t="n">
-        <v>0.76</v>
+        <v>-4.04</v>
       </c>
     </row>
     <row r="5">
@@ -3489,13 +3649,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>133</v>
+        <v>142.5</v>
       </c>
       <c r="C5" t="n">
-        <v>120.59</v>
+        <v>125.54</v>
       </c>
       <c r="D5" t="n">
-        <v>-12.41</v>
+        <v>-16.96</v>
       </c>
     </row>
   </sheetData>

--- a/sheet/8614.xlsx
+++ b/sheet/8614.xlsx
@@ -1214,10 +1214,10 @@
         <v>9</v>
       </c>
       <c r="G22" t="n">
-        <v>4.38</v>
+        <v>8.08</v>
       </c>
       <c r="H22" t="n">
-        <v>-4.62</v>
+        <v>-0.92</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1984,10 +1984,10 @@
         <v>9</v>
       </c>
       <c r="G43" t="n">
-        <v>2.98</v>
+        <v>6.68</v>
       </c>
       <c r="H43" t="n">
-        <v>-6.02</v>
+        <v>-2.32</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2764,10 +2764,10 @@
         <v>9.5</v>
       </c>
       <c r="G64" t="n">
-        <v>4.7</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="H64" t="n">
-        <v>-4.8</v>
+        <v>-0.88</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -3544,10 +3544,10 @@
         <v>9.5</v>
       </c>
       <c r="G85" t="n">
-        <v>4.95</v>
+        <v>8.82</v>
       </c>
       <c r="H85" t="n">
-        <v>-4.55</v>
+        <v>-0.68</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -3604,10 +3604,10 @@
         <v>133</v>
       </c>
       <c r="C2" t="n">
-        <v>109.08</v>
+        <v>112.78</v>
       </c>
       <c r="D2" t="n">
-        <v>-23.92</v>
+        <v>-20.22</v>
       </c>
     </row>
     <row r="3">
@@ -3620,10 +3620,10 @@
         <v>134</v>
       </c>
       <c r="C3" t="n">
-        <v>109.42</v>
+        <v>113.12</v>
       </c>
       <c r="D3" t="n">
-        <v>-24.58</v>
+        <v>-20.88</v>
       </c>
     </row>
     <row r="4">
@@ -3636,10 +3636,10 @@
         <v>142.5</v>
       </c>
       <c r="C4" t="n">
-        <v>138.46</v>
+        <v>142.38</v>
       </c>
       <c r="D4" t="n">
-        <v>-4.04</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="5">
@@ -3652,10 +3652,10 @@
         <v>142.5</v>
       </c>
       <c r="C5" t="n">
-        <v>125.54</v>
+        <v>129.41</v>
       </c>
       <c r="D5" t="n">
-        <v>-16.96</v>
+        <v>-13.09</v>
       </c>
     </row>
   </sheetData>

--- a/sheet/8614.xlsx
+++ b/sheet/8614.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J85"/>
+  <dimension ref="A1:J113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1230,15 +1230,15 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>496</v>
+        <v>486</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BERDIN, GILLYZA L [6565]</t>
+          <t>BERDIN, DENISE G [6595]</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>46143</v>
+        <v>46164</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1254,10 +1254,10 @@
         <v>9</v>
       </c>
       <c r="G23" t="n">
-        <v>8.92</v>
+        <v>9.16</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.08</v>
+        <v>0.16</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1270,15 +1270,15 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>497</v>
+        <v>487</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BERDIN, GILLYZA L [6565]</t>
+          <t>BERDIN, DENISE G [6595]</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>46144</v>
+        <v>46165</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -1300,15 +1300,15 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>498</v>
+        <v>488</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BERDIN, GILLYZA L [6565]</t>
+          <t>BERDIN, DENISE G [6595]</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>46145</v>
+        <v>46166</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -1330,15 +1330,15 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>499</v>
+        <v>489</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BERDIN, GILLYZA L [6565]</t>
+          <t>BERDIN, DENISE G [6595]</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>46146</v>
+        <v>46167</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1354,10 +1354,10 @@
         <v>9</v>
       </c>
       <c r="G26" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.1</v>
+        <v>-9</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1370,15 +1370,15 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BERDIN, GILLYZA L [6565]</t>
+          <t>BERDIN, DENISE G [6595]</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>46147</v>
+        <v>46168</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1394,10 +1394,10 @@
         <v>9</v>
       </c>
       <c r="G27" t="n">
-        <v>8.93</v>
+        <v>8.43</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.57</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1410,15 +1410,15 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>501</v>
+        <v>491</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BERDIN, GILLYZA L [6565]</t>
+          <t>BERDIN, DENISE G [6595]</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>46148</v>
+        <v>46169</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1434,10 +1434,10 @@
         <v>9</v>
       </c>
       <c r="G28" t="n">
-        <v>8.6</v>
+        <v>10.52</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.4</v>
+        <v>1.52</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1450,15 +1450,15 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BERDIN, GILLYZA L [6565]</t>
+          <t>BERDIN, DENISE G [6595]</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>46149</v>
+        <v>46170</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1474,10 +1474,10 @@
         <v>9</v>
       </c>
       <c r="G29" t="n">
-        <v>8.869999999999999</v>
+        <v>4.72</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.13</v>
+        <v>-4.28</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>46150</v>
+        <v>46143</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1514,10 +1514,10 @@
         <v>9</v>
       </c>
       <c r="G30" t="n">
-        <v>8.869999999999999</v>
+        <v>8.92</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.13</v>
+        <v>-0.08</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>46151</v>
+        <v>46144</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -1560,7 +1560,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>46152</v>
+        <v>46145</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -1590,7 +1590,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>46153</v>
+        <v>46146</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1614,10 +1614,10 @@
         <v>9</v>
       </c>
       <c r="G33" t="n">
-        <v>8.949999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>46154</v>
+        <v>46147</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1654,10 +1654,10 @@
         <v>9</v>
       </c>
       <c r="G34" t="n">
-        <v>9.140000000000001</v>
+        <v>8.93</v>
       </c>
       <c r="H34" t="n">
-        <v>0.14</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>46155</v>
+        <v>46148</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1694,10 +1694,10 @@
         <v>9</v>
       </c>
       <c r="G35" t="n">
-        <v>9.050000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="H35" t="n">
-        <v>0.05</v>
+        <v>-0.4</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1718,16 +1718,26 @@
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>46156</v>
+        <v>46149</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>06:30 PM</t>
+        </is>
       </c>
       <c r="F36" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G36" t="n">
-        <v>8</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>-0.13</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -1740,7 +1750,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1748,7 +1758,7 @@
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>46157</v>
+        <v>46150</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1764,10 +1774,10 @@
         <v>9</v>
       </c>
       <c r="G37" t="n">
-        <v>9.050000000000001</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="H37" t="n">
-        <v>0.05</v>
+        <v>-0.13</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -1780,7 +1790,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -1788,7 +1798,7 @@
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>46158</v>
+        <v>46151</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -1810,7 +1820,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -1818,7 +1828,7 @@
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>46159</v>
+        <v>46152</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -1840,7 +1850,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -1848,7 +1858,7 @@
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>46160</v>
+        <v>46153</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1864,10 +1874,10 @@
         <v>9</v>
       </c>
       <c r="G40" t="n">
-        <v>9.16</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="H40" t="n">
-        <v>0.16</v>
+        <v>-0.05</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -1880,7 +1890,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -1888,7 +1898,7 @@
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>46161</v>
+        <v>46154</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1904,10 +1914,10 @@
         <v>9</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="H41" t="n">
-        <v>-9</v>
+        <v>0.14</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -1920,7 +1930,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -1928,7 +1938,7 @@
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>46162</v>
+        <v>46155</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -1944,10 +1954,10 @@
         <v>9</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="H42" t="n">
-        <v>-9</v>
+        <v>0.05</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -1960,7 +1970,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -1968,26 +1978,16 @@
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>46163</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>06:30 PM</t>
-        </is>
+        <v>46156</v>
       </c>
       <c r="F43" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G43" t="n">
-        <v>6.68</v>
+        <v>8</v>
       </c>
       <c r="H43" t="n">
-        <v>-2.32</v>
+        <v>0</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2000,19 +2000,19 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>1705</v>
+        <v>510</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>LAO, ZYRA M [1144]</t>
+          <t>BERDIN, GILLYZA L [6565]</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>46143</v>
+        <v>46157</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>08:30 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2021,13 +2021,13 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="G44" t="n">
-        <v>9.74</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="H44" t="n">
-        <v>0.24</v>
+        <v>0.05</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2040,15 +2040,15 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1706</v>
+        <v>511</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>LAO, ZYRA M [1144]</t>
+          <t>BERDIN, GILLYZA L [6565]</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>46144</v>
+        <v>46158</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -2070,15 +2070,15 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1707</v>
+        <v>512</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>LAO, ZYRA M [1144]</t>
+          <t>BERDIN, GILLYZA L [6565]</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>46145</v>
+        <v>46159</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -2100,19 +2100,19 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1708</v>
+        <v>513</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>LAO, ZYRA M [1144]</t>
+          <t>BERDIN, GILLYZA L [6565]</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>46146</v>
+        <v>46160</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>08:30 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2121,13 +2121,13 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="G47" t="n">
-        <v>9.550000000000001</v>
+        <v>9.16</v>
       </c>
       <c r="H47" t="n">
-        <v>0.05</v>
+        <v>0.16</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2140,19 +2140,19 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1709</v>
+        <v>514</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>LAO, ZYRA M [1144]</t>
+          <t>BERDIN, GILLYZA L [6565]</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>46147</v>
+        <v>46161</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>08:30 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2161,13 +2161,13 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="G48" t="n">
-        <v>9.550000000000001</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.05</v>
+        <v>-9</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2180,19 +2180,19 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1710</v>
+        <v>515</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>LAO, ZYRA M [1144]</t>
+          <t>BERDIN, GILLYZA L [6565]</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>46148</v>
+        <v>46162</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>08:30 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2201,13 +2201,13 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="G49" t="n">
-        <v>9.050000000000001</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.45</v>
+        <v>-9</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2220,19 +2220,19 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1711</v>
+        <v>516</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>LAO, ZYRA M [1144]</t>
+          <t>BERDIN, GILLYZA L [6565]</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>46149</v>
+        <v>46163</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>08:30 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2241,13 +2241,13 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="G50" t="n">
-        <v>9.5</v>
+        <v>6.68</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>-2.32</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -2260,19 +2260,19 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1712</v>
+        <v>517</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>LAO, ZYRA M [1144]</t>
+          <t>BERDIN, GILLYZA L [6565]</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
-        <v>46150</v>
+        <v>46164</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>08:30 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2281,13 +2281,13 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="G51" t="n">
-        <v>9.630000000000001</v>
+        <v>9.18</v>
       </c>
       <c r="H51" t="n">
-        <v>0.13</v>
+        <v>0.18</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -2300,15 +2300,15 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1713</v>
+        <v>518</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>LAO, ZYRA M [1144]</t>
+          <t>BERDIN, GILLYZA L [6565]</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>46151</v>
+        <v>46165</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -2330,15 +2330,15 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1714</v>
+        <v>519</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>LAO, ZYRA M [1144]</t>
+          <t>BERDIN, GILLYZA L [6565]</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>46152</v>
+        <v>46166</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
@@ -2360,19 +2360,19 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>1715</v>
+        <v>520</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>LAO, ZYRA M [1144]</t>
+          <t>BERDIN, GILLYZA L [6565]</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>46153</v>
+        <v>46167</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>08:30 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2381,13 +2381,13 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="G54" t="n">
-        <v>9.529999999999999</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0.03</v>
+        <v>-9</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -2400,19 +2400,19 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>1716</v>
+        <v>521</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>LAO, ZYRA M [1144]</t>
+          <t>BERDIN, GILLYZA L [6565]</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
-        <v>46154</v>
+        <v>46168</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>08:30 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2421,13 +2421,13 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="G55" t="n">
-        <v>9.800000000000001</v>
+        <v>9.25</v>
       </c>
       <c r="H55" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -2440,19 +2440,19 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>1717</v>
+        <v>522</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>LAO, ZYRA M [1144]</t>
+          <t>BERDIN, GILLYZA L [6565]</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>46155</v>
+        <v>46169</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>08:30 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2461,13 +2461,13 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="G56" t="n">
-        <v>9.73</v>
+        <v>10.57</v>
       </c>
       <c r="H56" t="n">
-        <v>0.23</v>
+        <v>1.57</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -2480,19 +2480,19 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>1718</v>
+        <v>523</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>LAO, ZYRA M [1144]</t>
+          <t>BERDIN, GILLYZA L [6565]</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>46156</v>
+        <v>46170</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>08:30 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2501,13 +2501,13 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="G57" t="n">
-        <v>9.43</v>
+        <v>4.8</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-4.2</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>1719</v>
+        <v>1674</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>46157</v>
+        <v>46143</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         <v>9.5</v>
       </c>
       <c r="G58" t="n">
-        <v>9.890000000000001</v>
+        <v>9.74</v>
       </c>
       <c r="H58" t="n">
-        <v>0.39</v>
+        <v>0.24</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>1720</v>
+        <v>1675</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         </is>
       </c>
       <c r="C59" s="2" t="n">
-        <v>46158</v>
+        <v>46144</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
@@ -2590,7 +2590,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>1721</v>
+        <v>1676</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         </is>
       </c>
       <c r="C60" s="2" t="n">
-        <v>46159</v>
+        <v>46145</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
@@ -2620,7 +2620,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>1722</v>
+        <v>1677</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         </is>
       </c>
       <c r="C61" s="2" t="n">
-        <v>46160</v>
+        <v>46146</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -2644,10 +2644,10 @@
         <v>9.5</v>
       </c>
       <c r="G61" t="n">
-        <v>9.5</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>1723</v>
+        <v>1678</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="C62" s="2" t="n">
-        <v>46161</v>
+        <v>46147</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -2684,10 +2684,10 @@
         <v>9.5</v>
       </c>
       <c r="G62" t="n">
-        <v>9.449999999999999</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.05</v>
+        <v>0.05</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>1724</v>
+        <v>1679</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         </is>
       </c>
       <c r="C63" s="2" t="n">
-        <v>46162</v>
+        <v>46148</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -2724,10 +2724,10 @@
         <v>9.5</v>
       </c>
       <c r="G63" t="n">
-        <v>9.41</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.09</v>
+        <v>-0.45</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>1725</v>
+        <v>1680</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         </is>
       </c>
       <c r="C64" s="2" t="n">
-        <v>46163</v>
+        <v>46149</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -2764,10 +2764,10 @@
         <v>9.5</v>
       </c>
       <c r="G64" t="n">
-        <v>8.619999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.88</v>
+        <v>0</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -2780,34 +2780,34 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>3658</v>
+        <v>1681</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
+          <t>LAO, ZYRA M [1144]</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
-        <v>46143</v>
+        <v>46150</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>07:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F65" t="n">
         <v>9.5</v>
       </c>
       <c r="G65" t="n">
-        <v>6.34</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="H65" t="n">
-        <v>-3.16</v>
+        <v>0.13</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -2820,15 +2820,15 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>3659</v>
+        <v>1682</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
+          <t>LAO, ZYRA M [1144]</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
-        <v>46144</v>
+        <v>46151</v>
       </c>
       <c r="F66" t="n">
         <v>0</v>
@@ -2850,15 +2850,15 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>3660</v>
+        <v>1683</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
+          <t>LAO, ZYRA M [1144]</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
-        <v>46145</v>
+        <v>46152</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
@@ -2880,34 +2880,34 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>3661</v>
+        <v>1684</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
+          <t>LAO, ZYRA M [1144]</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
-        <v>46146</v>
+        <v>46153</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>07:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F68" t="n">
         <v>9.5</v>
       </c>
       <c r="G68" t="n">
-        <v>6.67</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="H68" t="n">
-        <v>-2.83</v>
+        <v>0.03</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -2920,34 +2920,34 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>3662</v>
+        <v>1685</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
+          <t>LAO, ZYRA M [1144]</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
-        <v>46147</v>
+        <v>46154</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>07:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F69" t="n">
         <v>9.5</v>
       </c>
       <c r="G69" t="n">
-        <v>8.18</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H69" t="n">
-        <v>-1.32</v>
+        <v>0.3</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -2960,34 +2960,34 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>3663</v>
+        <v>1686</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
+          <t>LAO, ZYRA M [1144]</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
-        <v>46148</v>
+        <v>46155</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>07:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F70" t="n">
         <v>9.5</v>
       </c>
       <c r="G70" t="n">
-        <v>8.550000000000001</v>
+        <v>9.73</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.95</v>
+        <v>0.23</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -3000,34 +3000,34 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>3664</v>
+        <v>1687</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
+          <t>LAO, ZYRA M [1144]</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
-        <v>46149</v>
+        <v>46156</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>07:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F71" t="n">
         <v>9.5</v>
       </c>
       <c r="G71" t="n">
-        <v>8.800000000000001</v>
+        <v>9.43</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.7</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -3040,34 +3040,34 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>3665</v>
+        <v>1688</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
+          <t>LAO, ZYRA M [1144]</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
-        <v>46150</v>
+        <v>46157</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>07:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F72" t="n">
         <v>9.5</v>
       </c>
       <c r="G72" t="n">
-        <v>8.77</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.73</v>
+        <v>0.39</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -3080,15 +3080,15 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>3666</v>
+        <v>1689</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
+          <t>LAO, ZYRA M [1144]</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
-        <v>46151</v>
+        <v>46158</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -3110,15 +3110,15 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>3667</v>
+        <v>1690</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
+          <t>LAO, ZYRA M [1144]</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
@@ -3140,34 +3140,34 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>3668</v>
+        <v>1691</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
+          <t>LAO, ZYRA M [1144]</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>07:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F75" t="n">
         <v>9.5</v>
       </c>
       <c r="G75" t="n">
-        <v>8.869999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="H75" t="n">
-        <v>-0.63</v>
+        <v>0</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -3180,34 +3180,34 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>3669</v>
+        <v>1692</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
+          <t>LAO, ZYRA M [1144]</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
-        <v>46154</v>
+        <v>46161</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>07:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F76" t="n">
         <v>9.5</v>
       </c>
       <c r="G76" t="n">
-        <v>10.23</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="H76" t="n">
-        <v>0.73</v>
+        <v>-0.05</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -3220,34 +3220,34 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>3670</v>
+        <v>1693</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
+          <t>LAO, ZYRA M [1144]</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
-        <v>46155</v>
+        <v>46162</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>07:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F77" t="n">
         <v>9.5</v>
       </c>
       <c r="G77" t="n">
-        <v>9.630000000000001</v>
+        <v>9.41</v>
       </c>
       <c r="H77" t="n">
-        <v>0.13</v>
+        <v>-0.09</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -3260,34 +3260,34 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>3671</v>
+        <v>1694</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
+          <t>LAO, ZYRA M [1144]</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
-        <v>46156</v>
+        <v>46163</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>07:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F78" t="n">
         <v>9.5</v>
       </c>
       <c r="G78" t="n">
-        <v>9.449999999999999</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="H78" t="n">
-        <v>-0.05</v>
+        <v>-0.88</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -3300,34 +3300,34 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>3672</v>
+        <v>1695</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
+          <t>LAO, ZYRA M [1144]</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
-        <v>46157</v>
+        <v>46164</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>07:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F79" t="n">
         <v>9.5</v>
       </c>
       <c r="G79" t="n">
-        <v>9.74</v>
+        <v>9.77</v>
       </c>
       <c r="H79" t="n">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -3340,15 +3340,15 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>3673</v>
+        <v>1696</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
+          <t>LAO, ZYRA M [1144]</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
-        <v>46158</v>
+        <v>46165</v>
       </c>
       <c r="F80" t="n">
         <v>0</v>
@@ -3370,15 +3370,15 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>3674</v>
+        <v>1697</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
+          <t>LAO, ZYRA M [1144]</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
-        <v>46159</v>
+        <v>46166</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
@@ -3400,34 +3400,34 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>3675</v>
+        <v>1698</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
+          <t>LAO, ZYRA M [1144]</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>07:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F82" t="n">
         <v>9.5</v>
       </c>
       <c r="G82" t="n">
-        <v>8.529999999999999</v>
+        <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>-0.97</v>
+        <v>-9.5</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -3440,34 +3440,34 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>3676</v>
+        <v>1699</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
+          <t>LAO, ZYRA M [1144]</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
-        <v>46161</v>
+        <v>46168</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>07:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F83" t="n">
         <v>9.5</v>
       </c>
       <c r="G83" t="n">
-        <v>8.279999999999999</v>
+        <v>9.76</v>
       </c>
       <c r="H83" t="n">
-        <v>-1.22</v>
+        <v>0.26</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -3480,34 +3480,34 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>3677</v>
+        <v>1700</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
+          <t>LAO, ZYRA M [1144]</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
-        <v>46162</v>
+        <v>46169</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>07:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F84" t="n">
         <v>9.5</v>
       </c>
       <c r="G84" t="n">
-        <v>8.550000000000001</v>
+        <v>9.52</v>
       </c>
       <c r="H84" t="n">
-        <v>-0.95</v>
+        <v>0.02</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -3520,41 +3520,1081 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>3678</v>
+        <v>1701</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>VILLAROMAN, JAMIE [1164]</t>
+          <t>LAO, ZYRA M [1144]</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
-        <v>46163</v>
+        <v>46170</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>09:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>07:00 PM</t>
+          <t>06:30 PM</t>
         </is>
       </c>
       <c r="F85" t="n">
         <v>9.5</v>
       </c>
       <c r="G85" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="H85" t="n">
+        <v>-4.65</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>3658</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G86" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="H86" t="n">
+        <v>-3.16</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>3659</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>3660</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>3661</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G89" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="H89" t="n">
+        <v>-2.83</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>3662</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G90" t="n">
+        <v>8.18</v>
+      </c>
+      <c r="H90" t="n">
+        <v>-1.32</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>3663</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G91" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="H91" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J91" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>3664</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G92" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="H92" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J92" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>3665</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G93" t="n">
+        <v>8.77</v>
+      </c>
+      <c r="H93" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J93" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>3666</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J94" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>3667</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J95" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>3668</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G96" t="n">
+        <v>8.869999999999999</v>
+      </c>
+      <c r="H96" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J96" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>3669</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G97" t="n">
+        <v>10.23</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J97" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>3670</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="n">
+        <v>46155</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G98" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J98" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>3671</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G99" t="n">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="H99" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J99" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>3672</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G100" t="n">
+        <v>9.74</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J100" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>3673</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J101" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>3674</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J102" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>3675</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G103" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="H103" t="n">
+        <v>-0.97</v>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J103" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>3676</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G104" t="n">
+        <v>8.279999999999999</v>
+      </c>
+      <c r="H104" t="n">
+        <v>-1.22</v>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J104" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>3677</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G105" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="H105" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J105" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>3678</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G106" t="n">
         <v>8.82</v>
       </c>
-      <c r="H85" t="n">
+      <c r="H106" t="n">
         <v>-0.68</v>
       </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>Avatco Inc - Camille Lopez de Leon</t>
-        </is>
-      </c>
-      <c r="J85" t="n">
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J106" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>3679</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G107" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="H107" t="n">
+        <v>-3.83</v>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J107" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>3680</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="F108" t="n">
+        <v>0</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J108" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>3681</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J109" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>3682</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="n">
+        <v>46167</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J110" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>3683</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="n">
+        <v>46168</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G111" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="H111" t="n">
+        <v>-1.08</v>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J111" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>3684</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="n">
+        <v>46169</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G112" t="n">
+        <v>10.15</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J112" t="n">
+        <v>8614</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>3685</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>VILLAROMAN, JAMIE [1164]</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="n">
+        <v>46170</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G113" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="H113" t="n">
+        <v>-4.67</v>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Avatco Inc - Camille Lopez de Leon</t>
+        </is>
+      </c>
+      <c r="J113" t="n">
         <v>8614</v>
       </c>
     </row>
@@ -3601,13 +4641,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>133</v>
+        <v>178</v>
       </c>
       <c r="C2" t="n">
-        <v>112.78</v>
+        <v>145.61</v>
       </c>
       <c r="D2" t="n">
-        <v>-20.22</v>
+        <v>-32.39</v>
       </c>
     </row>
     <row r="3">
@@ -3617,13 +4657,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>134</v>
+        <v>179</v>
       </c>
       <c r="C3" t="n">
-        <v>113.12</v>
+        <v>146.92</v>
       </c>
       <c r="D3" t="n">
-        <v>-20.88</v>
+        <v>-32.08</v>
       </c>
     </row>
     <row r="4">
@@ -3633,13 +4673,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>142.5</v>
+        <v>190</v>
       </c>
       <c r="C4" t="n">
-        <v>142.38</v>
+        <v>176.28</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.12</v>
+        <v>-13.72</v>
       </c>
     </row>
     <row r="5">
@@ -3649,13 +4689,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>142.5</v>
+        <v>190</v>
       </c>
       <c r="C5" t="n">
-        <v>129.41</v>
+        <v>158.48</v>
       </c>
       <c r="D5" t="n">
-        <v>-13.09</v>
+        <v>-31.52</v>
       </c>
     </row>
   </sheetData>

--- a/sheet/8614.xlsx
+++ b/sheet/8614.xlsx
@@ -1134,10 +1134,10 @@
         <v>9</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>13.98</v>
       </c>
       <c r="H20" t="n">
-        <v>-9</v>
+        <v>4.98</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1174,10 +1174,10 @@
         <v>9</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H21" t="n">
-        <v>-9</v>
+        <v>3</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2164,10 +2164,10 @@
         <v>9</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>13.98</v>
       </c>
       <c r="H48" t="n">
-        <v>-9</v>
+        <v>4.98</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2204,10 +2204,10 @@
         <v>9</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H49" t="n">
-        <v>-9</v>
+        <v>3</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -4644,10 +4644,10 @@
         <v>178</v>
       </c>
       <c r="C2" t="n">
-        <v>145.61</v>
+        <v>171.59</v>
       </c>
       <c r="D2" t="n">
-        <v>-32.39</v>
+        <v>-6.409999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -4660,10 +4660,10 @@
         <v>179</v>
       </c>
       <c r="C3" t="n">
-        <v>146.92</v>
+        <v>172.9</v>
       </c>
       <c r="D3" t="n">
-        <v>-32.08</v>
+        <v>-6.1</v>
       </c>
     </row>
     <row r="4">

--- a/sheet/8614.xlsx
+++ b/sheet/8614.xlsx
@@ -1474,10 +1474,10 @@
         <v>9</v>
       </c>
       <c r="G29" t="n">
-        <v>4.72</v>
+        <v>8.85</v>
       </c>
       <c r="H29" t="n">
-        <v>-4.28</v>
+        <v>-0.15</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2504,10 +2504,10 @@
         <v>9</v>
       </c>
       <c r="G57" t="n">
-        <v>4.8</v>
+        <v>8.82</v>
       </c>
       <c r="H57" t="n">
-        <v>-4.2</v>
+        <v>-0.18</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -3544,10 +3544,10 @@
         <v>9.5</v>
       </c>
       <c r="G85" t="n">
-        <v>4.85</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="H85" t="n">
-        <v>-4.65</v>
+        <v>0.03</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -4644,10 +4644,10 @@
         <v>178</v>
       </c>
       <c r="C2" t="n">
-        <v>171.59</v>
+        <v>175.72</v>
       </c>
       <c r="D2" t="n">
-        <v>-6.409999999999999</v>
+        <v>-2.279999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -4660,10 +4660,10 @@
         <v>179</v>
       </c>
       <c r="C3" t="n">
-        <v>172.9</v>
+        <v>176.92</v>
       </c>
       <c r="D3" t="n">
-        <v>-6.1</v>
+        <v>-2.08</v>
       </c>
     </row>
     <row r="4">
@@ -4676,10 +4676,10 @@
         <v>190</v>
       </c>
       <c r="C4" t="n">
-        <v>176.28</v>
+        <v>180.96</v>
       </c>
       <c r="D4" t="n">
-        <v>-13.72</v>
+        <v>-9.039999999999999</v>
       </c>
     </row>
     <row r="5">
